--- a/materials/record-templates/Electrochemical_Record_Template_v1.xlsx
+++ b/materials/record-templates/Electrochemical_Record_Template_v1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Record" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Electrochemical experiment record · 按导师模板 B 区设计（详见 docs/record-template-design.md）</t>
+          <t>电化学（无分室）实验记录 · 行级初始浓度长表（2026-10-17 重设计）</t>
         </is>
       </c>
     </row>
@@ -537,104 +537,116 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>初始浓度 (mg/L)：______</t>
+          <t>温度 (degC)：______</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>温度 (degC)：______</t>
+          <t>电解池配置 (Cell configuration)：______</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>电解池配置 (Cell configuration)：______</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
           <t>备注 / 检测仪器：______</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>【离子名】测量数据</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>【离子名】测量数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Time (s)</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Initial Concentration (mg/L)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Potential (V)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Current (A)</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Concentration (mg/L)</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>填写说明</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>填写说明</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>1) 把数据块标题中的【离子名】替换为实际目标离子（如 SO4、Cl、Na），保留【】括号。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>1) 把数据块标题中的【离子名】替换为实际目标离子（如 SO4、Cl、Na）。</t>
+          <t>2) 同一数据块记录多个初始浓度（多轮实验）的结果：按轮次顺序连排，Initial Concentration 列每行填写该轮初始浓度；同一轮的时间序列从 0 开始连续记录。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2) 数据从表头下方第一行开始连续填写，不要留空行；未测量的点留空（不要写 NA/ND）。</t>
+          <t>3) 块内不要留空行；不要把不同初始浓度并列成多列；未测量的点留空（不要写 NA/ND）。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3) 多离子实验：复制整个数据块（标题行 + 表头行 + 数据行），每离子一块，块间保留 3 行空行。</t>
+          <t>4) 多离子实验：复制整个数据块（标题行 + 表头行 + 数据行），每离子一块，块间保留 3 行空行。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>4) 实验信息区每行只写在最左侧一格内，不要拆到多列。</t>
+          <t>5) 实验信息区每行只写在最左侧一格内，不要拆到多列。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>5) 时间单位为秒 (s)；只记录原始测量值；电流密度、电荷量等由系统自动计算。</t>
+          <t>6) 时间单位为秒 (s)；只记录原始测量值；终浓度、去除率、电荷量、能耗等由系统按「离子 × 初始浓度」分组自动计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>7) 本表为无分室电解池设计；若实验有膜分室，请改用两室 / 三室 / 双极膜记录表。</t>
         </is>
       </c>
     </row>
